--- a/tables_filled/d6e2935c-8dea-4018-ba6c-8f2046a40386.xlsx
+++ b/tables_filled/d6e2935c-8dea-4018-ba6c-8f2046a40386.xlsx
@@ -17,6 +17,1240 @@
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="88">
+  <si>
+    <t>Referenz 1</t>
+  </si>
+  <si>
+    <t>Referenz 3</t>
+  </si>
+  <si>
+    <t>Referenz 2</t>
+  </si>
+  <si>
+    <t>Referenz 4</t>
+  </si>
+  <si>
+    <t>Referenz 5</t>
+  </si>
+  <si>
+    <t>Referenzbezeichnung:</t>
+  </si>
+  <si>
+    <t>Lfd. Referenz-Nr.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Allgemeine Mindeststandards, die mit </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>jeder</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Unternehmensreferenz nachgewiesen werden müssen:</t>
+    </r>
+  </si>
+  <si>
+    <t>Angabe der von dem anderen Unternehmen zu erbringenden Leistungen (Sofern zutreffend):</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Bauherr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Referenzgeber</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 
+(Name, Anschrift, Kontaktdaten):</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neben den Angaben in diesem Formblatt ist je Unternehmensreferenz eine Referenzbeschreibung vorzulegen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sofern die vom Bieter benannten Unternehmensreferenzen die Mindeststandards nicht erfüllen, wird das Angebot ausgeschlossen.
+</t>
+  </si>
+  <si>
+    <t>Ja / Nein</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soweit die Leistungen bei dem Referenzobjekt ganz oder teilweise von einem anderen Unternehmen erbracht wurden, gilt das jeweilige Kriterium als erfüllt, wenn das andere Unternehmen als Unterauftragnehmer im gegenständlichen Bauvorhaben entsprechenden Leistungen erbringen soll.
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Referenzinhaber</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (insb. im Falle von Bietergemeinschaften, Eignungsleihe mit Unterauftragnahme = anderes Unternehmen):</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Name des Bieters / Bietergemeischaft (BiGe)
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Referenzbeschreibung</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (nach eigenem Format) als Anlage:</t>
+    </r>
+  </si>
+  <si>
+    <t>Referenzschreiben vom AG als Anlage (sofern verfügbar):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Das Referenzobjekt beinhaltete die Planung einer Strangsanierung.
+</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Angabe </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>LP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Technische Ausrüstung:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bauliche </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fertigstellung</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Datum):
+Sofern laufend: Angabe Abschluss LP / vsl. Fertigstellung:</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Anforderungen der Auftraggeberin gemäß Auftragsbekanntmachung Ziff. III.1.3 Technische und berufliche Leistungsfähigkeit (1) Unternehmensreferenzen
+</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Angaben des Bieters zu Unternehmensreferenzen
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Das Formblatt ist elektronisch auszufüllen und als</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Excel-Datei</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> zurück zu geben.</t>
+    </r>
+  </si>
+  <si>
+    <t>Angabe:</t>
+  </si>
+  <si>
+    <t>- Das Referenzobjekt beinhalteten die Integration erneuerbaren Energien (Photovoltaik oder Solarthermie oder Geothermie oder Windkraft)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Das Referenzobjekt wurde im laufenden Betrieb umgesetzt und beinhaltete Provisorien und Interimsmaßnahmen zur Sicherstellung des Weiterbetriebs.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingenieur im Sinne des IngG des jeweiligen Bundeslandes </t>
+  </si>
+  <si>
+    <t>Durchschnitt der letzten 3 Jahre
+mindestens: 3.200.000 Euro</t>
+  </si>
+  <si>
+    <r>
+      <t>- Das Referenzobjekt beinhaltete Brandschutzmaßnahmen</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">im Bereich Versorgungstechnik.
+</t>
+    </r>
+  </si>
+  <si>
+    <t>Ja / Nein
+Angabe der Art der erneuerbaren Energie:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angaben zur wirtschaftlichen und finanziellen Leistungsfähigkeit:
+</t>
+  </si>
+  <si>
+    <t>allgemeiner jährlicher Umsatz bei einem geschätzten Auftragswert netto 6.379.200 Euro und einer Projektlaufzeit von 6 Jahren</t>
+  </si>
+  <si>
+    <t>Durchschnittliche Anzahl der beschäftigten Ingenieure (Bachelor / Master) der letzten drei Geschäftsjahre</t>
+  </si>
+  <si>
+    <t>mindestens: 5</t>
+  </si>
+  <si>
+    <t>Bemerkungen</t>
+  </si>
+  <si>
+    <t>HBr: Wichtige Vereinfachung</t>
+  </si>
+  <si>
+    <t>HBr: OK</t>
+  </si>
+  <si>
+    <t>HBr: Sollte nur bei Neubauten wegfallen</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">HBr: Dieses Kriterium wurde zumindest bei der OP oft "gerissen".
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Utru: hier TA ohne Einschränkung</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">HBr: LPH 8 wäre aus meiner Sicht wichtig. Sollte auch funktionieren, es wird ja kommuliert.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Utru: siehe Bewertungsmatrix</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">HBr: Schränkt den Wettbewerb ZUSÄTZLICH ein
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>utru: aber wir müssen Erneuerbare Energien anwenden!!</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Nachweis der Befähigung zur Berufsausübung / -Qualifikation
+eines Verantwortlichen
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>- Das Referenzobjekt (sämtliche Gebäudeteile) weist hinsichtlich der Sanierungs- und/oder Modernisierungsleistungen eine Bruttogrundfläche (BGF) nicht kleiner als 3</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="5"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.000</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> m²</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> auf.</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Angabe </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>BGF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> in m² der Sanierung/Modernisierung:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Für die Eignungsprüfung hat der Bieter mit dem Angebot anhand von mindestens 2 Unternehmensreferenzen aus den letzten 10 Jahren seine Erfahrung</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> mit Neubauprojekten in Mischprojekten mit klassischer Bauweise und Modulbauweise sowie Modernisierung und Sanierung von Bestandsbauten unter Berücksichtigung </t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">mit vergleichbaren Leistungen, d. h. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Fachplanungsleistungen Technische Ausrüstung unter Berücksichtigung der nachfolgend benannten Mindeststandards nachzuweisen.
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Referenzen sind sowohl für eine Sanierungs und/
+oder Modernisierungsmaßnahme als auch für eine
+Neubaumaßnahme unter Berücksichtigung der nachfolgend benannten
+Mindeststandards nachzuweisen </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">- Bauliche Fertigstellung der Neubau- bzw. Sanierungs- und/oder Modernisierungsmaßnahme nicht vor dem 01.01.2014 oder noch laufend </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(bei laufender Baumaßnahme: mindestens Abschluss der Leistungsphase (LP) 7 nach HOAI). Bei Kombination aus Sanierung/Modernisierung und Neubau ist die jeweilige bauliche Fertigstellung getrennt anzugeben. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <t>Weitere Mindeststandards, die kumuliert über die mindestens 2 Referenzen nachgewiesen werden müssen.</t>
+  </si>
+  <si>
+    <t>Fachplanungsleistungen lt. HOAI § 53 - Technische Ausrüstung i.S.d. Anlage 15.2 ab Honorarzone II mindestens der Anlagengruppen 1- 6. Der Nachweis der Anlagengruppen kann kumuliert eingereichten Referenzen erfolgen.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Angabe zu:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+- Anzahl Geschosse
+- Honorarzone</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Angaben zu:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+- Anlagengruppen</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>- Fachplanungsleistungen lt. HOAI § 53 - Technische Ausrüstung i.S.d. Anlage 15.2 HOAI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">für ein </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>mehrgeschossiges</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Hochbauobjekt mit</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Neubau- bzw.Sanierungs- und/oder Modernisierungsmaßnahmen.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">- Das Referenzobjekt beinhaltete die Leistungsphasen (LP) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>3 bis 8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (LP 4 nicht zwingend) der Technischen Ausrüstung nach HOAI, die mindestens schon einmal erbracht wurden.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Name des Bieters / Bietergemeischaft (BiGe)
+</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Baubeginn </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Sanierung/Mod.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Datum):
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Bauliche </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Fertigstellung</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Sanierung/Mod.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  (Datum):
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Anforderungen der Auftraggeberin gemäß Auftragsbekanntmachung Technische und berufliche Leistungsfähigkeit - Unternehmensreferenzen
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neben den Angaben in diesem Formblatt ist je Unternehmensreferenz eine aussagefähige Referenzbeschreibung (nach eigenem Format) vorzulegen.
+</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Fachplanungsleistungen lt. HOAI § 53 - Technische Ausrüstung i.S.d. Anlage 15.2 HOAI für ein </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>mehrgeschossiges</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Hochbauobjekt mit </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Sanierungs-/ Modernisierungsmaßnahmen
+ </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mindestens 1 Referenzobjekt beinhaltet die Integration </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>einer der genannten</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> erneuerbaren Energien (Photovoltaik oder Solarthermie oder Geothermie oder Windkraft), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">mindestens 1 Referenzobjekt </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Modernisierung / Sanierung</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> beinhaltete die Leistungsphasen</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (LPH) 6 bis</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">8 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">der Technischen Ausrüstung nach HOAI.
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">sofern laufend, Angabe Beginn LPH 8 und voraussichtliche Fertigstellung (Datum):
+</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Angabe </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">LPH </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Technische Ausrüstung:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Angabe </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>LPH</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Technische Ausrüstung:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Das Referenzobjekt </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Modernisierung / Sanierung</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> beinhaltete die Leistungsphasen</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (LPH) 2 bis 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Leistungsphase 4 nicht zwingend) der Technischen Ausrüstung nach HOAI</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Bauliche</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Fertigstellung </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">der </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Sanierungs- und/oder Modernisierungsmaßnahme</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> nicht vor dem 01.01.2016 oder bei noch laufender Baumaßnahme mindestens Beginn der Leistungsphase (LPH) 8 nach HOAI.
+(Ggf. getrennt nach Bauabschnitten / Bauteilen - sofern zutreffend.)
+</t>
+    </r>
+  </si>
+  <si>
+    <t>Mindestens 1 Referenzobjekt wurde mit einem öffentlichen Bauherrn gemäß § 98 GWB realisiert.</t>
+  </si>
+  <si>
+    <t>Mindestens 1 Referenzobjekt befand sich während der Bauphase im laufenden Betrieb</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Angaben zu:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+- Honorarzone:
+- Anlagengruppe:
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Fachplanungsleistungen lt. HOAI § 53 - Technische Ausrüstung i.S.d. Anlage 15.2 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ab Honorarzone II mindestens</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> der Anlagengruppen 1-5 und 8</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Soweit die Leistungen bei dem Referenzobjekt ganz oder teilweise von einem anderen Unternehmen erbracht wurden, gilt das jeweilige Kriterium als erfüllt, wenn das andere Unternehmen als Unterauftragnehmer / BiGe-Mitglied</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">im gegenständlichen Bauvorhaben entsprechenden Leistungen erbringen wird.
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Ort/Land:
+</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Angabe zu: 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Sanierung/Modernisierung Ja / Nein: Anzahl Geschosse:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">mindestens 1 Referenzobjekt hat eine BGF von &gt; 5000m²
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Referenzbeschreibung</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (nach eigenem Format) als Anlage:
+</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Referenzschreiben vom AG als Anlage (sofern verfügbar):
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Photovoltaik Ja / Nein 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solarthermie Ja / Nein
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geothermie Ja / Nein
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Windkraft Ja / Nein
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lfd. Referenz-Nr.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angaben zum Referenzformat
+</t>
+  </si>
+  <si>
+    <r>
+      <t>Weitere Mindeststandards, die ergänzend zu den Allgemeinen Mindeststandards (Zeile 10-14)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>kumuliert über die eingereichten Referenzen nachgewiesen werden müssen:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Für die Eignungsprüfung hat der Bieter mit dem Angebot anhand von </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">mindestens 2 Unternehmensreferenzen aus den letzten 10 Jahren </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>mit Ausführung innerhalb der Europäischen Union (EU) oder der Schweiz seine Erfahrung mit Fachplanungsleistungen Technische Ausrüstung für</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Sanierungs-/Modernisierungsmaßnahmen</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> von Bestandsbauten unter Berücksichtigung der nachfolgend benannten Mindeststandards nachzuweisen.
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Zusätzliche Mindeststandards, die über mindestens 1 Referenz nachgewiesen werden müssen. Hier können zusätzliche Referenzen benannt werden, welche die Allgemeinen</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Zeile 10-14) und Weiteren</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(Zeile 16-19) Mindeststandards nicht erfüllen müssen.
+Die benannten Referenzen müssen Hochbauobjekte sein.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Ja / Nein
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mindestens 1 Referenzobjekt beinhaltet eine Schadstoffsanierung im Schwarzbereich.
+</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1351,11 +2585,7 @@
 </t>
         </is>
       </c>
-      <c r="C2" s="137" t="inlineStr">
-        <is>
-          <t>Hansa Planungsgruppe GmbH</t>
-        </is>
-      </c>
+      <c r="C2" s="137" t="n"/>
       <c r="D2" s="138" t="n"/>
       <c r="E2" s="138" t="n"/>
       <c r="F2" s="138" t="n"/>
@@ -1524,27 +2754,27 @@
       </c>
       <c r="C7" s="82" t="inlineStr">
         <is>
-          <t>Hamburg, Deutschland</t>
+          <t>Hamburg, Germany</t>
         </is>
       </c>
       <c r="D7" s="82" t="inlineStr">
         <is>
-          <t>Hamburg, Deutschland</t>
+          <t>Hamburg, Germany</t>
         </is>
       </c>
       <c r="E7" s="82" t="inlineStr">
         <is>
-          <t>Lübeck, Deutschland</t>
+          <t>Lübeck, Germany</t>
         </is>
       </c>
       <c r="F7" s="82" t="inlineStr">
         <is>
-          <t>Hamburg, Deutschland</t>
+          <t>Hamburg, Germany</t>
         </is>
       </c>
       <c r="G7" s="82" t="inlineStr">
         <is>
-          <t>Hamburg, Deutschland</t>
+          <t>Hamburg, Germany</t>
         </is>
       </c>
     </row>
@@ -1595,27 +2825,27 @@
       </c>
       <c r="C10" s="82" t="inlineStr">
         <is>
-          <t>Ja / 5 Geschosse</t>
+          <t>Ja, 5 Geschosse</t>
         </is>
       </c>
       <c r="D10" s="82" t="inlineStr">
         <is>
-          <t>Ja / 6 Geschosse</t>
+          <t>Ja / 6</t>
         </is>
       </c>
       <c r="E10" s="82" t="inlineStr">
         <is>
-          <t>Ja / 6 Geschosse</t>
+          <t>Ja / 5</t>
         </is>
       </c>
       <c r="F10" s="82" t="inlineStr">
         <is>
-          <t>Ja / 5 Geschosse</t>
+          <t>Ja, 5</t>
         </is>
       </c>
       <c r="G10" s="82" t="inlineStr">
         <is>
-          <t>Ja / 4 Geschosse</t>
+          <t>Ja, 4 Geschosse</t>
         </is>
       </c>
     </row>
@@ -1635,27 +2865,27 @@
       </c>
       <c r="C11" s="83" t="inlineStr">
         <is>
-          <t>2020-2023</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="D11" s="83" t="inlineStr">
         <is>
-          <t>2019-2022</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="E11" s="83" t="inlineStr">
         <is>
-          <t>2021-2025</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="F11" s="83" t="inlineStr">
         <is>
-          <t>2018-2021</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="G11" s="82" t="inlineStr">
         <is>
-          <t>2017-2020</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="H11" s="86" t="n"/>
@@ -1681,12 +2911,12 @@
       <c r="E12" s="83" t="n"/>
       <c r="F12" s="83" t="inlineStr">
         <is>
-          <t>July 2021</t>
+          <t>Juli 2021</t>
         </is>
       </c>
       <c r="G12" s="82" t="inlineStr">
         <is>
-          <t>December 2020</t>
+          <t>Dezember 2020</t>
         </is>
       </c>
       <c r="H12" s="86" t="n"/>
@@ -1703,7 +2933,7 @@
       <c r="D13" s="83" t="n"/>
       <c r="E13" s="83" t="inlineStr">
         <is>
-          <t>LPH 8 started May 2025, expected full completion October 2026</t>
+          <t>Beginn LPH 8: Mai 2025, voraussichtliche Fertigstellung: Oktober 2026</t>
         </is>
       </c>
       <c r="F13" s="83" t="n"/>
@@ -1723,27 +2953,27 @@
       </c>
       <c r="C14" s="83" t="inlineStr">
         <is>
-          <t>Ja (LPH 2-5)</t>
+          <t>LPH 2-8</t>
         </is>
       </c>
       <c r="D14" s="83" t="inlineStr">
         <is>
-          <t>Ja (LPH 2-5)</t>
+          <t>LPH 2-8</t>
         </is>
       </c>
       <c r="E14" s="83" t="inlineStr">
         <is>
-          <t>Ja (LPH 2-5)</t>
+          <t>LPH 2-8</t>
         </is>
       </c>
       <c r="F14" s="83" t="inlineStr">
         <is>
-          <t>Ja (LPH 2-5)</t>
+          <t>LPH 2-8</t>
         </is>
       </c>
       <c r="G14" s="82" t="inlineStr">
         <is>
-          <t>Ja (LPH 2-5)</t>
+          <t>LPH 2-8</t>
         </is>
       </c>
       <c r="H14" s="80" t="n"/>
@@ -1776,27 +3006,27 @@
       </c>
       <c r="C16" s="82" t="inlineStr">
         <is>
-          <t>Ja (LPH 6-8)</t>
+          <t>LPH 2-8</t>
         </is>
       </c>
       <c r="D16" s="82" t="inlineStr">
         <is>
-          <t>Ja (LPH 6-8)</t>
+          <t>LPH 2-8</t>
         </is>
       </c>
       <c r="E16" s="82" t="inlineStr">
         <is>
-          <t>Ja (LPH 6-8)</t>
+          <t>LPH 2-8</t>
         </is>
       </c>
       <c r="F16" s="82" t="inlineStr">
         <is>
-          <t>Ja (LPH 6-8)</t>
+          <t>LPH 2-8</t>
         </is>
       </c>
       <c r="G16" s="82" t="inlineStr">
         <is>
-          <t>Ja (LPH 6-8)</t>
+          <t>LPH 2-8</t>
         </is>
       </c>
       <c r="H16" s="86" t="n"/>
@@ -1817,27 +3047,27 @@
       </c>
       <c r="C17" s="82" t="inlineStr">
         <is>
-          <t>HZ II-III, AG 1, 2, 3, 4, 5, 8</t>
+          <t>Honorarzone II-III, Anlagengruppen 1, 2, 3, 4, 5, 8</t>
         </is>
       </c>
       <c r="D17" s="82" t="inlineStr">
         <is>
-          <t>HZ II, AG 1, 2, 3, 7, 8</t>
+          <t>Honorarzone II / AG 1, 2, 3, 7, 8</t>
         </is>
       </c>
       <c r="E17" s="82" t="inlineStr">
         <is>
-          <t>HZ III, AG 1, 2, 3, 4, 5, 6, 8</t>
+          <t>Honorarzone III, Anlagengruppen 1, 2, 3, 4, 5, 6, 8</t>
         </is>
       </c>
       <c r="F17" s="82" t="inlineStr">
         <is>
-          <t>HZ III, AG 1, 2, 3, 4, 5, 8</t>
+          <t>Honorarzone III, AG 1, 2, 3, 4, 5, 8</t>
         </is>
       </c>
       <c r="G17" s="82" t="inlineStr">
         <is>
-          <t>HZ II-III, AG 1, 2, 3, 4, 5, 8</t>
+          <t>Honorarzone II-III, Anlagengruppen 1, 2, 3, 4, 5, 8</t>
         </is>
       </c>
       <c r="H17" s="86" t="n"/>
@@ -1859,26 +3089,14 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="D18" s="103" t="inlineStr">
+      <c r="D18" s="103" t="n"/>
+      <c r="E18" s="103" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="E18" s="103" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="F18" s="103" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="G18" s="103" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
+      <c r="F18" s="103" t="n"/>
+      <c r="G18" s="103" t="n"/>
       <c r="H18" s="86" t="n"/>
     </row>
     <row r="19" ht="30" customFormat="1" customHeight="1" s="101">
@@ -1910,7 +3128,7 @@
       </c>
       <c r="F19" s="104" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="G19" s="104" t="inlineStr">
@@ -1965,7 +3183,7 @@
       </c>
       <c r="F21" s="82" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="G21" s="82" t="inlineStr">
@@ -1999,7 +3217,7 @@
       </c>
       <c r="F22" s="82" t="inlineStr">
         <is>
-          <t>Nein</t>
+          <t>nein</t>
         </is>
       </c>
       <c r="G22" s="82" t="inlineStr">
@@ -2033,7 +3251,7 @@
       </c>
       <c r="F23" s="82" t="inlineStr">
         <is>
-          <t>Nein</t>
+          <t>nein</t>
         </is>
       </c>
       <c r="G23" s="82" t="inlineStr">
@@ -2067,7 +3285,7 @@
       </c>
       <c r="F24" s="82" t="inlineStr">
         <is>
-          <t>Nein</t>
+          <t>nein</t>
         </is>
       </c>
       <c r="G24" s="82" t="inlineStr">
@@ -2105,7 +3323,7 @@
       </c>
       <c r="F25" s="104" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="G25" s="104" t="inlineStr">
@@ -2143,7 +3361,7 @@
       </c>
       <c r="F26" s="104" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>ja</t>
         </is>
       </c>
       <c r="G26" s="104" t="inlineStr">
@@ -2185,21 +3403,13 @@
           <t>Ja</t>
         </is>
       </c>
-      <c r="D28" s="82" t="inlineStr">
+      <c r="D28" s="82" t="n"/>
+      <c r="E28" s="82" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="E28" s="82" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="F28" s="82" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
+      <c r="F28" s="82" t="n"/>
       <c r="G28" s="82" t="inlineStr">
         <is>
           <t>Ja</t>
@@ -2219,26 +3429,10 @@
           <t>Ja / Nein</t>
         </is>
       </c>
-      <c r="C29" s="82" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="D29" s="82" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="E29" s="82" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="F29" s="82" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
+      <c r="C29" s="82" t="n"/>
+      <c r="D29" s="82" t="n"/>
+      <c r="E29" s="82" t="n"/>
+      <c r="F29" s="82" t="n"/>
       <c r="G29" s="96" t="n"/>
       <c r="H29" s="81" t="n"/>
     </row>
